--- a/report_cards/Report_Card_Shakiru_Baraka.xlsx
+++ b/report_cards/Report_Card_Shakiru_Baraka.xlsx
@@ -1257,11 +1257,7 @@
           <t>Position in Class:</t>
         </is>
       </c>
-      <c r="M20" s="39" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
+      <c r="M20" s="39" t="inlineStr"/>
       <c r="N20" s="30" t="n"/>
       <c r="O20" s="30" t="n"/>
       <c r="P20" s="30" t="n"/>
@@ -1595,7 +1591,7 @@
       <c r="O29" s="36" t="n"/>
       <c r="P29" s="42" t="inlineStr">
         <is>
-          <t>9th</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="Q29" s="35" t="n"/>
@@ -1942,7 +1938,7 @@
       <c r="O36" s="36" t="n"/>
       <c r="P36" s="42" t="inlineStr">
         <is>
-          <t>5th</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="Q36" s="35" t="n"/>
@@ -2195,11 +2191,7 @@
           <t>Position in Class</t>
         </is>
       </c>
-      <c r="X42" s="43" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
+      <c r="X42" s="43" t="inlineStr"/>
       <c r="Y42" s="30" t="n"/>
       <c r="Z42" s="30" t="n"/>
     </row>
@@ -2565,11 +2557,7 @@
       <c r="D52" s="35" t="n"/>
       <c r="E52" s="35" t="n"/>
       <c r="F52" s="36" t="n"/>
-      <c r="G52" s="44" t="inlineStr">
-        <is>
-          <t>5th</t>
-        </is>
-      </c>
+      <c r="G52" s="44" t="inlineStr"/>
       <c r="H52" s="35" t="n"/>
       <c r="I52" s="35" t="n"/>
       <c r="J52" s="35" t="n"/>

--- a/report_cards/Report_Card_Shakiru_Baraka.xlsx
+++ b/report_cards/Report_Card_Shakiru_Baraka.xlsx
@@ -1530,7 +1530,7 @@
       <c r="O28" s="36" t="n"/>
       <c r="P28" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>5th</t>
         </is>
       </c>
       <c r="Q28" s="35" t="n"/>
@@ -2355,7 +2355,7 @@
       <c r="O46" s="36" t="n"/>
       <c r="P46" s="42" t="inlineStr">
         <is>
-          <t>2nd</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q46" s="35" t="n"/>

--- a/report_cards/Report_Card_Shakiru_Baraka.xlsx
+++ b/report_cards/Report_Card_Shakiru_Baraka.xlsx
@@ -1870,16 +1870,32 @@
       <c r="D35" s="35" t="n"/>
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
-      <c r="G35" s="18" t="inlineStr"/>
-      <c r="H35" s="18" t="inlineStr"/>
+      <c r="G35" s="42" t="n">
+        <v>11</v>
+      </c>
+      <c r="H35" s="42" t="n">
+        <v>16</v>
+      </c>
       <c r="I35" s="36" t="n"/>
-      <c r="J35" s="18" t="inlineStr"/>
+      <c r="J35" s="42" t="n">
+        <v>0</v>
+      </c>
       <c r="K35" s="36" t="n"/>
-      <c r="L35" s="18" t="inlineStr"/>
+      <c r="L35" s="18">
+        <f>SUM(G35, H35, J35)</f>
+        <v/>
+      </c>
       <c r="M35" s="36" t="n"/>
-      <c r="N35" s="18" t="inlineStr"/>
+      <c r="N35" s="18">
+        <f>IF(L35&gt;=75,"A1",IF(L35&gt;=70,"B2",IF(L35&gt;=65,"B3",IF(L35&gt;=60,"C4",IF(L35&gt;=55,"C5",IF(L35&gt;=50,"C6",IF(L35&gt;=45,"D7",IF(L35&gt;=40,"E8","F9"))))))))</f>
+        <v/>
+      </c>
       <c r="O35" s="36" t="n"/>
-      <c r="P35" s="18" t="inlineStr"/>
+      <c r="P35" s="42" t="inlineStr">
+        <is>
+          <t>10th</t>
+        </is>
+      </c>
       <c r="Q35" s="35" t="n"/>
       <c r="R35" s="36" t="n"/>
       <c r="T35" s="18" t="inlineStr">
@@ -2012,7 +2028,7 @@
         </is>
       </c>
       <c r="X38" s="43" t="n">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="Y38" s="30" t="n"/>
       <c r="Z38" s="30" t="n"/>
@@ -2064,7 +2080,7 @@
         </is>
       </c>
       <c r="X39" s="43" t="n">
-        <v>74</v>
+        <v>69.3</v>
       </c>
       <c r="Y39" s="30" t="n"/>
       <c r="Z39" s="30" t="n"/>
@@ -2101,7 +2117,7 @@
       </c>
       <c r="X40" s="43" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="Y40" s="30" t="n"/>
@@ -2139,7 +2155,7 @@
       </c>
       <c r="X41" s="43" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="Y41" s="30" t="n"/>
@@ -2314,7 +2330,7 @@
         </is>
       </c>
       <c r="X45" s="43" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="Y45" s="30" t="n"/>
       <c r="Z45" s="30" t="n"/>
@@ -2426,7 +2442,7 @@
       <c r="E48" s="35" t="n"/>
       <c r="F48" s="36" t="n"/>
       <c r="G48" s="44" t="n">
-        <v>666</v>
+        <v>693</v>
       </c>
       <c r="H48" s="35" t="n"/>
       <c r="I48" s="35" t="n"/>
@@ -2458,7 +2474,7 @@
       <c r="E49" s="35" t="n"/>
       <c r="F49" s="36" t="n"/>
       <c r="G49" s="44" t="n">
-        <v>74</v>
+        <v>69.3</v>
       </c>
       <c r="H49" s="35" t="n"/>
       <c r="I49" s="35" t="n"/>
@@ -2491,7 +2507,7 @@
       <c r="F50" s="36" t="n"/>
       <c r="G50" s="44" t="inlineStr">
         <is>
-          <t>74.0%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="H50" s="35" t="n"/>
@@ -2525,7 +2541,7 @@
       <c r="F51" s="36" t="n"/>
       <c r="G51" s="44" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="H51" s="35" t="n"/>
@@ -2634,7 +2650,7 @@
       <c r="E55" s="35" t="n"/>
       <c r="F55" s="36" t="n"/>
       <c r="G55" s="44" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="H55" s="35" t="n"/>
       <c r="I55" s="35" t="n"/>

--- a/report_cards/Report_Card_Shakiru_Baraka.xlsx
+++ b/report_cards/Report_Card_Shakiru_Baraka.xlsx
@@ -2247,7 +2247,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>

--- a/report_cards/Report_Card_Shakiru_Baraka.xlsx
+++ b/report_cards/Report_Card_Shakiru_Baraka.xlsx
@@ -1871,14 +1871,14 @@
       <c r="E35" s="35" t="n"/>
       <c r="F35" s="36" t="n"/>
       <c r="G35" s="42" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H35" s="42" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I35" s="36" t="n"/>
       <c r="J35" s="42" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K35" s="36" t="n"/>
       <c r="L35" s="18">
@@ -2247,7 +2247,7 @@
       <c r="O43" s="36" t="n"/>
       <c r="P43" s="42" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="Q43" s="35" t="n"/>
